--- a/Statistics/Section 2 - Descriptive Statistics Fundamentals/11_Covariance/Course notes/Covariance.xlsx
+++ b/Statistics/Section 2 - Descriptive Statistics Fundamentals/11_Covariance/Course notes/Covariance.xlsx
@@ -1,25 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="18229"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Iliya\Desktop\Statistics Course\Filming\Final excel\Section 2 - Descriptive statistics\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\slong\365 Data Science\Statistics_\Section 2 - Descriptive Statistics Fundamentals\11_Covariance_\Course notes\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00829E49-96DE-4806-98C6-D279B54AF401}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19320" windowHeight="7920"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Covariance" sheetId="13" r:id="rId1"/>
     <sheet name="cov" sheetId="10" state="hidden" r:id="rId2"/>
     <sheet name="Covariance2" sheetId="11" state="hidden" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="171027"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -58,11 +62,11 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
-    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="165" formatCode="#,##0_);\-\ #,##0_)"/>
+    <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="166" formatCode="#,##0_);\-\ #,##0_)"/>
   </numFmts>
   <fonts count="6" x14ac:knownFonts="1">
     <font>
@@ -153,7 +157,7 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -162,22 +166,22 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="2" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="43" fontId="2" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="43" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="2" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="2" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="2" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="166" fontId="2" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="2" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="2" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="43" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -2145,6 +2149,252 @@
     </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>131618</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>27709</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>609600</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>13855</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="TextBox 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{35266B8B-834F-4149-A32C-73D8876808F9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4696691" y="671945"/>
+          <a:ext cx="4842164" cy="2847110"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100" b="1" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Covariance</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t> is a way to measure how two different things</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100" b="0" i="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t> that</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t> change together</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100" b="0" i="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t> for example; the height of plants and the amount of watering they receive.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="en-GB" sz="1100" b="0" i="0" baseline="0">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100" b="1" i="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Positive covariance</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100" b="0" i="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>: The two things go up at the same time. The more hours you put in the better results you get</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="en-GB" sz="1100" b="0" i="0" baseline="0">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100" b="1"/>
+            <a:t>Negative covariance</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100"/>
+            <a:t>: The more time you put in A the less time you have for B</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="en-GB" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100" b="1"/>
+            <a:t>Zero</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100" b="1" baseline="0"/>
+            <a:t> covariance</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100" baseline="0"/>
+            <a:t>: A has not bearing on B</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-GB" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>394854</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>6927</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>282698</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>31925</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Picture 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5C04349E-072F-4A0B-97DD-7F40631A65EC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4959927" y="2341418"/>
+          <a:ext cx="3628571" cy="904762"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -2487,7 +2737,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="B1:H17"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="11.4" x14ac:dyDescent="0.2"/>
@@ -2676,7 +2926,7 @@
       <c r="H17" s="13"/>
     </row>
   </sheetData>
-  <sortState ref="G6:G14">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="G6:G14">
     <sortCondition descending="1" ref="G6"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2686,7 +2936,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet5"/>
   <dimension ref="B1:G16"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="11.4" x14ac:dyDescent="0.2"/>
@@ -2843,7 +3093,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Sheet6"/>
   <dimension ref="B1:G16"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="11.4" x14ac:dyDescent="0.2"/>
